--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -1282,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121004577</v>
+        <v>121004582</v>
       </c>
       <c r="B7" t="n">
-        <v>91963</v>
+        <v>89753</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,25 +1294,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550574</v>
+        <v>550413</v>
       </c>
       <c r="R7" t="n">
-        <v>6994485</v>
+        <v>6994537</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1391,7 +1391,7 @@
         <v>121004579</v>
       </c>
       <c r="B8" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121004576</v>
+        <v>121004572</v>
       </c>
       <c r="B9" t="n">
-        <v>78598</v>
+        <v>91973</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,25 +1506,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550574</v>
+        <v>550483</v>
       </c>
       <c r="R9" t="n">
-        <v>6994485</v>
+        <v>6994428</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1600,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121004582</v>
+        <v>121004576</v>
       </c>
       <c r="B10" t="n">
-        <v>89743</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,21 +1616,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550413</v>
+        <v>550574</v>
       </c>
       <c r="R10" t="n">
-        <v>6994537</v>
+        <v>6994485</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1706,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121004572</v>
+        <v>121004577</v>
       </c>
       <c r="B11" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550483</v>
+        <v>550574</v>
       </c>
       <c r="R11" t="n">
-        <v>6994428</v>
+        <v>6994485</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1815,7 +1815,7 @@
         <v>121004580</v>
       </c>
       <c r="B12" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>121004574</v>
       </c>
       <c r="B13" t="n">
-        <v>91955</v>
+        <v>91965</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -1282,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121004582</v>
+        <v>121004576</v>
       </c>
       <c r="B7" t="n">
-        <v>89753</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,21 +1298,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550413</v>
+        <v>550574</v>
       </c>
       <c r="R7" t="n">
-        <v>6994537</v>
+        <v>6994485</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121004579</v>
+        <v>121004582</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>89753</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,21 +1404,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550553</v>
+        <v>550413</v>
       </c>
       <c r="R8" t="n">
         <v>6994537</v>
@@ -1600,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121004576</v>
+        <v>121004579</v>
       </c>
       <c r="B10" t="n">
         <v>78601</v>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550574</v>
+        <v>550553</v>
       </c>
       <c r="R10" t="n">
-        <v>6994485</v>
+        <v>6994537</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -1282,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121004576</v>
+        <v>121004580</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>91985</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,25 +1294,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550574</v>
+        <v>550446</v>
       </c>
       <c r="R7" t="n">
-        <v>6994485</v>
+        <v>6994540</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121004582</v>
+        <v>121004576</v>
       </c>
       <c r="B8" t="n">
-        <v>89753</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,21 +1404,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550413</v>
+        <v>550574</v>
       </c>
       <c r="R8" t="n">
-        <v>6994537</v>
+        <v>6994485</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121004572</v>
+        <v>121004579</v>
       </c>
       <c r="B9" t="n">
-        <v>91973</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,25 +1506,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550483</v>
+        <v>550553</v>
       </c>
       <c r="R9" t="n">
-        <v>6994428</v>
+        <v>6994537</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1600,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121004579</v>
+        <v>121004582</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>89760</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,21 +1616,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550553</v>
+        <v>550413</v>
       </c>
       <c r="R10" t="n">
         <v>6994537</v>
@@ -1706,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121004577</v>
+        <v>121004572</v>
       </c>
       <c r="B11" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550574</v>
+        <v>550483</v>
       </c>
       <c r="R11" t="n">
-        <v>6994485</v>
+        <v>6994428</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121004580</v>
+        <v>121004577</v>
       </c>
       <c r="B12" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550446</v>
+        <v>550574</v>
       </c>
       <c r="R12" t="n">
-        <v>6994540</v>
+        <v>6994485</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1921,7 +1921,7 @@
         <v>121004574</v>
       </c>
       <c r="B13" t="n">
-        <v>91965</v>
+        <v>91977</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -1921,7 +1921,7 @@
         <v>121004574</v>
       </c>
       <c r="B13" t="n">
-        <v>91977</v>
+        <v>91978</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -1921,7 +1921,7 @@
         <v>121004574</v>
       </c>
       <c r="B13" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2022,6 +2022,1261 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126098889</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92522</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>550414</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6994562</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126098329</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>550325</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6994462</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rik förekomst vid björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126098914</v>
+      </c>
+      <c r="B16" t="n">
+        <v>75062</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>310</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nordlig nållav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenotheca laevigata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>550461</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6994538</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126098379</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92522</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>550364</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6994541</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126098335</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98360</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>550326</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6994473</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126098314</v>
+      </c>
+      <c r="B19" t="n">
+        <v>82784</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>550342</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6994466</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126098363</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>550365</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6994523</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126098423</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>550359</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6994564</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126098483</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80035</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>550359</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6994564</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126099190</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80075</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>550528</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6994556</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126098349</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78639</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>353</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>550332</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6994514</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På grov tallåga</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126098507</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80110</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>550359</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6994564</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -2024,37 +2024,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126098889</v>
+        <v>126098329</v>
       </c>
       <c r="B14" t="n">
-        <v>92522</v>
+        <v>98339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2062,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550414</v>
+        <v>550325</v>
       </c>
       <c r="R14" t="n">
-        <v>6994562</v>
+        <v>6994462</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2102,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>Rik förekomst vid björkhögstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,38 +2131,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126098329</v>
+        <v>126098889</v>
       </c>
       <c r="B15" t="n">
-        <v>98339</v>
+        <v>92522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550325</v>
+        <v>550414</v>
       </c>
       <c r="R15" t="n">
-        <v>6994462</v>
+        <v>6994562</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rik förekomst vid björkhögstubbe</t>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2024,38 +2024,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126098329</v>
+        <v>126098889</v>
       </c>
       <c r="B14" t="n">
-        <v>98339</v>
+        <v>92522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2063,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550325</v>
+        <v>550414</v>
       </c>
       <c r="R14" t="n">
-        <v>6994462</v>
+        <v>6994562</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2102,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rik förekomst vid björkhögstubbe</t>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,37 +2130,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126098889</v>
+        <v>126098329</v>
       </c>
       <c r="B15" t="n">
-        <v>92522</v>
+        <v>98339</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550414</v>
+        <v>550325</v>
       </c>
       <c r="R15" t="n">
-        <v>6994562</v>
+        <v>6994462</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>Rik förekomst vid björkhögstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3277,6 +3277,107 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126152097</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91393</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>550473</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6994545</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -2027,7 +2027,7 @@
         <v>126098329</v>
       </c>
       <c r="B14" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>126098889</v>
       </c>
       <c r="B15" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,32 +2237,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126098914</v>
+        <v>126098379</v>
       </c>
       <c r="B16" t="n">
-        <v>75062</v>
+        <v>92524</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>310</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550461</v>
+        <v>550364</v>
       </c>
       <c r="R16" t="n">
-        <v>6994538</v>
+        <v>6994541</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På tallåga</t>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,32 +2343,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126098379</v>
+        <v>126098914</v>
       </c>
       <c r="B17" t="n">
-        <v>92522</v>
+        <v>75063</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550364</v>
+        <v>550461</v>
       </c>
       <c r="R17" t="n">
-        <v>6994541</v>
+        <v>6994538</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,7 +2452,7 @@
         <v>126098335</v>
       </c>
       <c r="B18" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126098314</v>
       </c>
       <c r="B19" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>126098363</v>
       </c>
       <c r="B20" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,38 +2753,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126098423</v>
+        <v>126098483</v>
       </c>
       <c r="B21" t="n">
-        <v>98339</v>
+        <v>80036</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2828,6 +2827,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,37 +2859,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126098483</v>
+        <v>126098423</v>
       </c>
       <c r="B22" t="n">
-        <v>80035</v>
+        <v>98341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2929,11 +2934,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2964,7 +2964,7 @@
         <v>126099190</v>
       </c>
       <c r="B23" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>126098349</v>
       </c>
       <c r="B24" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>126098507</v>
       </c>
       <c r="B25" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>126152097</v>
       </c>
       <c r="B26" t="n">
-        <v>91393</v>
+        <v>91395</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -2753,37 +2753,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126098483</v>
+        <v>126098423</v>
       </c>
       <c r="B21" t="n">
-        <v>80036</v>
+        <v>98341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2827,11 +2828,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2859,38 +2855,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126098423</v>
+        <v>126098483</v>
       </c>
       <c r="B22" t="n">
-        <v>98341</v>
+        <v>80036</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2934,6 +2929,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -2024,38 +2024,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126098329</v>
+        <v>126098889</v>
       </c>
       <c r="B14" t="n">
-        <v>98341</v>
+        <v>92526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2063,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550325</v>
+        <v>550414</v>
       </c>
       <c r="R14" t="n">
-        <v>6994462</v>
+        <v>6994562</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2102,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rik förekomst vid björkhögstubbe</t>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,37 +2130,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126098889</v>
+        <v>126098329</v>
       </c>
       <c r="B15" t="n">
-        <v>92524</v>
+        <v>98343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550414</v>
+        <v>550325</v>
       </c>
       <c r="R15" t="n">
-        <v>6994562</v>
+        <v>6994462</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>Rik förekomst vid björkhögstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,7 +2240,7 @@
         <v>126098379</v>
       </c>
       <c r="B16" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>126098335</v>
       </c>
       <c r="B18" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>126098423</v>
       </c>
       <c r="B21" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>126152097</v>
       </c>
       <c r="B26" t="n">
-        <v>91395</v>
+        <v>91397</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -2027,7 +2027,7 @@
         <v>126098889</v>
       </c>
       <c r="B14" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>126098329</v>
       </c>
       <c r="B15" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>126098379</v>
       </c>
       <c r="B16" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>126098335</v>
       </c>
       <c r="B18" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>126098423</v>
       </c>
       <c r="B21" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>126152097</v>
       </c>
       <c r="B26" t="n">
-        <v>91397</v>
+        <v>91399</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -2024,37 +2024,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126098889</v>
+        <v>126098329</v>
       </c>
       <c r="B14" t="n">
-        <v>92528</v>
+        <v>98345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2062,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550414</v>
+        <v>550325</v>
       </c>
       <c r="R14" t="n">
-        <v>6994562</v>
+        <v>6994462</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2102,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>Rik förekomst vid björkhögstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,38 +2131,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126098329</v>
+        <v>126098889</v>
       </c>
       <c r="B15" t="n">
-        <v>98345</v>
+        <v>92528</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550325</v>
+        <v>550414</v>
       </c>
       <c r="R15" t="n">
-        <v>6994462</v>
+        <v>6994562</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rik förekomst vid björkhögstubbe</t>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -2024,38 +2024,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126098329</v>
+        <v>126098889</v>
       </c>
       <c r="B14" t="n">
-        <v>98345</v>
+        <v>92532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2063,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550325</v>
+        <v>550414</v>
       </c>
       <c r="R14" t="n">
-        <v>6994462</v>
+        <v>6994562</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2102,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rik förekomst vid björkhögstubbe</t>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,37 +2130,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126098889</v>
+        <v>126098329</v>
       </c>
       <c r="B15" t="n">
-        <v>92528</v>
+        <v>98349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550414</v>
+        <v>550325</v>
       </c>
       <c r="R15" t="n">
-        <v>6994562</v>
+        <v>6994462</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>Rik förekomst vid björkhögstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,7 +2240,7 @@
         <v>126098379</v>
       </c>
       <c r="B16" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>126098914</v>
       </c>
       <c r="B17" t="n">
-        <v>75063</v>
+        <v>75067</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>126098335</v>
       </c>
       <c r="B18" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126098314</v>
       </c>
       <c r="B19" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>126098363</v>
       </c>
       <c r="B20" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,38 +2753,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126098423</v>
+        <v>126098483</v>
       </c>
       <c r="B21" t="n">
-        <v>98345</v>
+        <v>80040</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2828,6 +2827,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,37 +2859,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126098483</v>
+        <v>126098423</v>
       </c>
       <c r="B22" t="n">
-        <v>80036</v>
+        <v>98349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2929,11 +2934,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2964,7 +2964,7 @@
         <v>126099190</v>
       </c>
       <c r="B23" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>126098349</v>
       </c>
       <c r="B24" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>126098507</v>
       </c>
       <c r="B25" t="n">
-        <v>80111</v>
+        <v>80115</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>126152097</v>
       </c>
       <c r="B26" t="n">
-        <v>91399</v>
+        <v>91403</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -2237,32 +2237,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126098379</v>
+        <v>126098914</v>
       </c>
       <c r="B16" t="n">
-        <v>92532</v>
+        <v>75067</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550364</v>
+        <v>550461</v>
       </c>
       <c r="R16" t="n">
-        <v>6994541</v>
+        <v>6994538</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,32 +2343,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126098914</v>
+        <v>126098379</v>
       </c>
       <c r="B17" t="n">
-        <v>75067</v>
+        <v>92532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>310</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550461</v>
+        <v>550364</v>
       </c>
       <c r="R17" t="n">
-        <v>6994538</v>
+        <v>6994541</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På tallåga</t>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -2024,37 +2024,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126098889</v>
+        <v>126098329</v>
       </c>
       <c r="B14" t="n">
-        <v>92532</v>
+        <v>98352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2062,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550414</v>
+        <v>550325</v>
       </c>
       <c r="R14" t="n">
-        <v>6994562</v>
+        <v>6994462</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2102,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>Rik förekomst vid björkhögstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,38 +2131,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126098329</v>
+        <v>126098889</v>
       </c>
       <c r="B15" t="n">
-        <v>98349</v>
+        <v>92532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550325</v>
+        <v>550414</v>
       </c>
       <c r="R15" t="n">
-        <v>6994462</v>
+        <v>6994562</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rik förekomst vid björkhögstubbe</t>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2452,7 +2452,7 @@
         <v>126098335</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2753,37 +2753,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126098483</v>
+        <v>126098423</v>
       </c>
       <c r="B21" t="n">
-        <v>80040</v>
+        <v>98352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2827,11 +2828,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2859,38 +2855,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126098423</v>
+        <v>126098483</v>
       </c>
       <c r="B22" t="n">
-        <v>98349</v>
+        <v>80040</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2934,6 +2929,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -2024,38 +2024,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126098329</v>
+        <v>126098889</v>
       </c>
       <c r="B14" t="n">
-        <v>98352</v>
+        <v>92532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2063,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550325</v>
+        <v>550414</v>
       </c>
       <c r="R14" t="n">
-        <v>6994462</v>
+        <v>6994562</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2102,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rik förekomst vid björkhögstubbe</t>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,37 +2130,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126098889</v>
+        <v>126098329</v>
       </c>
       <c r="B15" t="n">
-        <v>92532</v>
+        <v>98352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550414</v>
+        <v>550325</v>
       </c>
       <c r="R15" t="n">
-        <v>6994562</v>
+        <v>6994462</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>Rik förekomst vid björkhögstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,32 +2237,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126098914</v>
+        <v>126098379</v>
       </c>
       <c r="B16" t="n">
-        <v>75067</v>
+        <v>92532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>310</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550461</v>
+        <v>550364</v>
       </c>
       <c r="R16" t="n">
-        <v>6994538</v>
+        <v>6994541</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På tallåga</t>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,32 +2343,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126098379</v>
+        <v>126098914</v>
       </c>
       <c r="B17" t="n">
-        <v>92532</v>
+        <v>75067</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550364</v>
+        <v>550461</v>
       </c>
       <c r="R17" t="n">
-        <v>6994541</v>
+        <v>6994538</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -2237,32 +2237,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126098379</v>
+        <v>126098914</v>
       </c>
       <c r="B16" t="n">
-        <v>92532</v>
+        <v>75067</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550364</v>
+        <v>550461</v>
       </c>
       <c r="R16" t="n">
-        <v>6994541</v>
+        <v>6994538</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,32 +2343,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126098914</v>
+        <v>126098379</v>
       </c>
       <c r="B17" t="n">
-        <v>75067</v>
+        <v>92532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>310</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550461</v>
+        <v>550364</v>
       </c>
       <c r="R17" t="n">
-        <v>6994538</v>
+        <v>6994541</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På tallåga</t>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2753,38 +2753,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126098423</v>
+        <v>126098483</v>
       </c>
       <c r="B21" t="n">
-        <v>98352</v>
+        <v>80040</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2828,6 +2827,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,37 +2859,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126098483</v>
+        <v>126098423</v>
       </c>
       <c r="B22" t="n">
-        <v>80040</v>
+        <v>98352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2929,11 +2934,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -2753,37 +2753,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126098483</v>
+        <v>126098423</v>
       </c>
       <c r="B21" t="n">
-        <v>80040</v>
+        <v>98352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2827,11 +2828,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2859,38 +2855,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126098423</v>
+        <v>126098483</v>
       </c>
       <c r="B22" t="n">
-        <v>98352</v>
+        <v>80040</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2934,6 +2929,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -2024,37 +2024,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126098889</v>
+        <v>126098329</v>
       </c>
       <c r="B14" t="n">
-        <v>92532</v>
+        <v>98361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2062,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550414</v>
+        <v>550325</v>
       </c>
       <c r="R14" t="n">
-        <v>6994562</v>
+        <v>6994462</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2102,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>Rik förekomst vid björkhögstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,38 +2131,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126098329</v>
+        <v>126098889</v>
       </c>
       <c r="B15" t="n">
-        <v>98352</v>
+        <v>92535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550325</v>
+        <v>550414</v>
       </c>
       <c r="R15" t="n">
-        <v>6994462</v>
+        <v>6994562</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rik förekomst vid björkhögstubbe</t>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,7 +2240,7 @@
         <v>126098914</v>
       </c>
       <c r="B16" t="n">
-        <v>75067</v>
+        <v>75070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>126098379</v>
       </c>
       <c r="B17" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>126098335</v>
       </c>
       <c r="B18" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126098314</v>
       </c>
       <c r="B19" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>126098363</v>
       </c>
       <c r="B20" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,38 +2753,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126098423</v>
+        <v>126098483</v>
       </c>
       <c r="B21" t="n">
-        <v>98352</v>
+        <v>80043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2828,6 +2827,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,37 +2859,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126098483</v>
+        <v>126098423</v>
       </c>
       <c r="B22" t="n">
-        <v>80040</v>
+        <v>98361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2929,11 +2934,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2964,7 +2964,7 @@
         <v>126099190</v>
       </c>
       <c r="B23" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>126098349</v>
       </c>
       <c r="B24" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>126098507</v>
       </c>
       <c r="B25" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>126152097</v>
       </c>
       <c r="B26" t="n">
-        <v>91403</v>
+        <v>91406</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -2024,38 +2024,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126098329</v>
+        <v>126098889</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>92535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2063,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550325</v>
+        <v>550414</v>
       </c>
       <c r="R14" t="n">
-        <v>6994462</v>
+        <v>6994562</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2102,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rik förekomst vid björkhögstubbe</t>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,37 +2130,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126098889</v>
+        <v>126098329</v>
       </c>
       <c r="B15" t="n">
-        <v>92535</v>
+        <v>98361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550414</v>
+        <v>550325</v>
       </c>
       <c r="R15" t="n">
-        <v>6994562</v>
+        <v>6994462</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>Rik förekomst vid björkhögstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2753,37 +2753,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126098483</v>
+        <v>126098423</v>
       </c>
       <c r="B21" t="n">
-        <v>80043</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2827,11 +2828,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2859,38 +2855,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126098423</v>
+        <v>126098483</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>80043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2934,6 +2929,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -2753,38 +2753,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126098423</v>
+        <v>126098483</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>80043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2828,6 +2827,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,37 +2859,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126098483</v>
+        <v>126098423</v>
       </c>
       <c r="B22" t="n">
-        <v>80043</v>
+        <v>98361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2929,11 +2934,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -2753,37 +2753,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126098483</v>
+        <v>126098423</v>
       </c>
       <c r="B21" t="n">
-        <v>80043</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2827,11 +2828,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2859,38 +2855,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126098423</v>
+        <v>126098483</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>80043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2934,6 +2929,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3378,6 +3378,588 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134246409</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93254</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>550472</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6994595</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134246407</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79115</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>550434</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6994476</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134246412</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80473</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>550551</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6994539</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134246411</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>550551</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6994539</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134246413</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>550559</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6994526</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134246410</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>550482</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6994611</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -3383,7 +3383,7 @@
         <v>134246409</v>
       </c>
       <c r="B27" t="n">
-        <v>93254</v>
+        <v>93256</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>134246407</v>
       </c>
       <c r="B28" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>134246412</v>
       </c>
       <c r="B29" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,32 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134246411</v>
+        <v>134246413</v>
       </c>
       <c r="B30" t="n">
-        <v>80477</v>
+        <v>79359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550551</v>
+        <v>550559</v>
       </c>
       <c r="R30" t="n">
-        <v>6994539</v>
+        <v>6994526</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3768,32 +3768,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134246413</v>
+        <v>134246411</v>
       </c>
       <c r="B31" t="n">
-        <v>79358</v>
+        <v>80478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550559</v>
+        <v>550551</v>
       </c>
       <c r="R31" t="n">
-        <v>6994526</v>
+        <v>6994539</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3868,7 +3868,7 @@
         <v>134246410</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>79117</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -3383,7 +3383,7 @@
         <v>134246409</v>
       </c>
       <c r="B27" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>134246407</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>134246413</v>
       </c>
       <c r="B29" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,32 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134246412</v>
+        <v>134246411</v>
       </c>
       <c r="B30" t="n">
-        <v>80474</v>
+        <v>80485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3768,32 +3768,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134246411</v>
+        <v>134246412</v>
       </c>
       <c r="B31" t="n">
-        <v>80478</v>
+        <v>80481</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3868,7 +3868,7 @@
         <v>134246410</v>
       </c>
       <c r="B32" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62025587</v>
+        <v>126098914</v>
       </c>
       <c r="B2" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550466.4299713583</v>
+        <v>550461</v>
       </c>
       <c r="R2" t="n">
-        <v>6994615.315636201</v>
+        <v>6994538</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,43 +762,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Grov tallåga</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62025586</v>
+        <v>62025587</v>
       </c>
       <c r="B3" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550466.4299713583</v>
+        <v>550466</v>
       </c>
       <c r="R3" t="n">
-        <v>6994615.315636201</v>
+        <v>6994615</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,21 +849,11 @@
           <t>2016-07-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-07-06</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,7 +870,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Gammal tall</t>
+          <t>Grov tallåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,15 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103996049</v>
+        <v>103996101</v>
       </c>
       <c r="B4" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550474.371032651</v>
+        <v>550466</v>
       </c>
       <c r="R4" t="n">
-        <v>6994542.464097296</v>
+        <v>6994537</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +958,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +968,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,15 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103996058</v>
+        <v>126098349</v>
       </c>
       <c r="B5" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,37 +1015,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartabbortjärnen, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550472.116211893</v>
+        <v>550332</v>
       </c>
       <c r="R5" t="n">
-        <v>6994541.522503904</v>
+        <v>6994514</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,22 +1072,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På grov tallåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,13 +1091,9 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1150,26 +1103,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103996101</v>
+        <v>126098314</v>
       </c>
       <c r="B6" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,37 +1121,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartabbortjärnen, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550465.3728776035</v>
+        <v>550342</v>
       </c>
       <c r="R6" t="n">
-        <v>6994537.33826041</v>
+        <v>6994466</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,22 +1178,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,13 +1192,9 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1271,48 +1204,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121004580</v>
+        <v>126152097</v>
       </c>
       <c r="B7" t="n">
-        <v>91985</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1321,14 +1245,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550446</v>
+        <v>550473</v>
       </c>
       <c r="R7" t="n">
-        <v>6994540</v>
+        <v>6994545</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,12 +1279,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,15 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121004576</v>
+        <v>121004582</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1431,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550574</v>
+        <v>550413</v>
       </c>
       <c r="R8" t="n">
-        <v>6994485</v>
+        <v>6994537</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1494,15 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121004579</v>
+        <v>121004574</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,21 +1424,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1537,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550553</v>
+        <v>550601</v>
       </c>
       <c r="R9" t="n">
-        <v>6994537</v>
+        <v>6994490</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1600,15 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121004582</v>
+        <v>121004572</v>
       </c>
       <c r="B10" t="n">
-        <v>89760</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550413</v>
+        <v>550483</v>
       </c>
       <c r="R10" t="n">
-        <v>6994537</v>
+        <v>6994428</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1706,19 +1615,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121004572</v>
+        <v>121004577</v>
       </c>
       <c r="B11" t="n">
-        <v>91985</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1749,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550483</v>
+        <v>550574</v>
       </c>
       <c r="R11" t="n">
-        <v>6994428</v>
+        <v>6994485</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1812,19 +1716,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121004577</v>
+        <v>121004580</v>
       </c>
       <c r="B12" t="n">
-        <v>91985</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1855,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550574</v>
+        <v>550446</v>
       </c>
       <c r="R12" t="n">
-        <v>6994485</v>
+        <v>6994540</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1918,15 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121004574</v>
+        <v>126098379</v>
       </c>
       <c r="B13" t="n">
-        <v>91981</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,14 +1851,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550601</v>
+        <v>550364</v>
       </c>
       <c r="R13" t="n">
-        <v>6994490</v>
+        <v>6994541</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,12 +1885,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,11 +1926,11 @@
         <v>126098889</v>
       </c>
       <c r="B14" t="n">
-        <v>92535</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2130,52 +2029,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126098329</v>
+        <v>134246409</v>
       </c>
       <c r="B15" t="n">
-        <v>98361</v>
+        <v>93271</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550325</v>
+        <v>550472</v>
       </c>
       <c r="R15" t="n">
-        <v>6994462</v>
+        <v>6994595</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2199,17 +2094,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rik förekomst vid björkhögstubbe</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2218,51 +2108,50 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126098914</v>
+        <v>121004576</v>
       </c>
       <c r="B16" t="n">
-        <v>75070</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,14 +2160,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550461</v>
+        <v>550574</v>
       </c>
       <c r="R16" t="n">
-        <v>6994538</v>
+        <v>6994485</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2305,17 +2194,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,32 +2227,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126098379</v>
+        <v>121004579</v>
       </c>
       <c r="B17" t="n">
-        <v>92535</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2377,14 +2261,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550364</v>
+        <v>550553</v>
       </c>
       <c r="R17" t="n">
-        <v>6994541</v>
+        <v>6994537</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2411,17 +2295,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2449,52 +2328,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126098335</v>
+        <v>134246413</v>
       </c>
       <c r="B18" t="n">
-        <v>98382</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550326</v>
+        <v>550559</v>
       </c>
       <c r="R18" t="n">
-        <v>6994473</v>
+        <v>6994526</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2518,12 +2393,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2532,29 +2407,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126098314</v>
+        <v>103996050</v>
       </c>
       <c r="B19" t="n">
-        <v>82792</v>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,40 +2436,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Svartabbortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550342</v>
+        <v>550561</v>
       </c>
       <c r="R19" t="n">
-        <v>6994466</v>
+        <v>6994584</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2619,12 +2490,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2633,9 +2514,13 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2645,17 +2530,21 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126098363</v>
+        <v>134246407</v>
       </c>
       <c r="B20" t="n">
-        <v>78739</v>
+        <v>79130</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,40 +2552,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550365</v>
+        <v>550434</v>
       </c>
       <c r="R20" t="n">
-        <v>6994523</v>
+        <v>6994476</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2720,12 +2606,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2734,70 +2620,66 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126098483</v>
+        <v>103996058</v>
       </c>
       <c r="B21" t="n">
-        <v>80043</v>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Svartabbortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550359</v>
+        <v>550472</v>
       </c>
       <c r="R21" t="n">
-        <v>6994564</v>
+        <v>6994541</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2821,17 +2703,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2840,9 +2727,13 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2852,45 +2743,48 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126098423</v>
+        <v>126099190</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2898,10 +2792,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550359</v>
+        <v>550528</v>
       </c>
       <c r="R22" t="n">
-        <v>6994564</v>
+        <v>6994556</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2934,6 +2828,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2961,10 +2860,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126099190</v>
+        <v>134246412</v>
       </c>
       <c r="B23" t="n">
-        <v>80083</v>
+        <v>80488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2990,22 +2889,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550528</v>
+        <v>550551</v>
       </c>
       <c r="R23" t="n">
-        <v>6994556</v>
+        <v>6994539</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3029,17 +2925,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3048,70 +2939,66 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126098349</v>
+        <v>134246411</v>
       </c>
       <c r="B24" t="n">
-        <v>78647</v>
+        <v>80492</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550332</v>
+        <v>550551</v>
       </c>
       <c r="R24" t="n">
-        <v>6994514</v>
+        <v>6994539</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3135,17 +3022,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På grov tallåga</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,19 +3036,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3176,7 +3057,7 @@
         <v>126098507</v>
       </c>
       <c r="B25" t="n">
-        <v>80118</v>
+        <v>80467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3279,51 +3160,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126152097</v>
+        <v>62025586</v>
       </c>
       <c r="B26" t="n">
-        <v>91406</v>
+        <v>5495</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1503</v>
+        <v>101410</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550473</v>
+        <v>550466</v>
       </c>
       <c r="R26" t="n">
-        <v>6994545</v>
+        <v>6994615</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3347,12 +3225,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3361,67 +3239,80 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Gammal tall</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134246409</v>
+        <v>126098329</v>
       </c>
       <c r="B27" t="n">
-        <v>93264</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550472</v>
+        <v>550325</v>
       </c>
       <c r="R27" t="n">
-        <v>6994595</v>
+        <v>6994462</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,12 +3336,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rik förekomst vid björkhögstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3459,66 +3355,71 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134246407</v>
+        <v>126098423</v>
       </c>
       <c r="B28" t="n">
-        <v>79123</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550434</v>
+        <v>550359</v>
       </c>
       <c r="R28" t="n">
-        <v>6994476</v>
+        <v>6994564</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3542,12 +3443,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3556,66 +3457,71 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134246413</v>
+        <v>126098335</v>
       </c>
       <c r="B29" t="n">
-        <v>79366</v>
+        <v>99140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550559</v>
+        <v>550326</v>
       </c>
       <c r="R29" t="n">
-        <v>6994526</v>
+        <v>6994473</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3639,12 +3545,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3653,63 +3559,64 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134246411</v>
+        <v>103996049</v>
       </c>
       <c r="B30" t="n">
-        <v>80485</v>
+        <v>79085</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Svartabbortjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550551</v>
+        <v>550474</v>
       </c>
       <c r="R30" t="n">
-        <v>6994539</v>
+        <v>6994542</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,12 +3643,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3752,26 +3669,35 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134246412</v>
+        <v>126098363</v>
       </c>
       <c r="B31" t="n">
-        <v>80481</v>
+        <v>79085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,37 +3705,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550551</v>
+        <v>550365</v>
       </c>
       <c r="R31" t="n">
-        <v>6994539</v>
+        <v>6994523</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3833,12 +3762,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3847,18 +3776,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3868,7 +3798,7 @@
         <v>134246410</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>79131</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3959,6 +3889,112 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126098483</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skog ca 500 m öster om Lappbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>550359</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6994564</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41415-2024 artfynd.xlsx
+++ b/artfynd/A 41415-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126098914</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025587</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103996101</t>
         </is>
       </c>
     </row>
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126098349</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126098314</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126152097</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004582</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004574</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1612,6 +1657,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004572</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1713,6 +1763,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004577</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,6 +1869,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004580</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1920,6 +1980,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126098379</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2026,6 +2091,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126098889</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2123,6 +2193,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246409</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2224,6 +2299,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004576</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2325,6 +2405,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004579</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2422,6 +2507,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246413</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2538,6 +2628,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103996050</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2635,6 +2730,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246407</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2749,6 +2849,11 @@
       <c r="AY21" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103996058</t>
         </is>
       </c>
     </row>
@@ -2857,6 +2962,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126099190</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2954,6 +3064,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246412</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3051,6 +3166,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246411</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3157,6 +3277,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126098507</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3264,6 +3389,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025586</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3371,6 +3501,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126098329</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3473,6 +3608,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126098423</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3575,6 +3715,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126098335</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3689,6 +3834,11 @@
       <c r="AY30" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103996049</t>
         </is>
       </c>
     </row>
@@ -3792,6 +3942,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126098363</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3889,6 +4044,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246410</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3995,8 +4155,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126098483</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>